--- a/src/main/resources/i18n/excel.xlsx
+++ b/src/main/resources/i18n/excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Micro\PracticeBasic\src\main\resources\i18n\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\User-Service\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA5B181-173D-4A60-B627-B0A4CAD44AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54990D93-7D7F-4F74-B83A-769BE9C76A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="6495" yWindow="1710" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>key</t>
   </si>
@@ -138,6 +138,45 @@
   </si>
   <si>
     <t>{0} {1} はアクティブです</t>
+  </si>
+  <si>
+    <t>DEPARTMENT_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Department is not found</t>
+  </si>
+  <si>
+    <t>Không tìm thấy bưu cục</t>
+  </si>
+  <si>
+    <t>部門が見つかりません</t>
+  </si>
+  <si>
+    <t>TTCN</t>
+  </si>
+  <si>
+    <t>Information Technology Center</t>
+  </si>
+  <si>
+    <t>Trung tâm công nghệ</t>
+  </si>
+  <si>
+    <t>情報技術センター</t>
+  </si>
+  <si>
+    <t>TTR01</t>
+  </si>
+  <si>
+    <t>Bưu cục Thanh Trì</t>
+  </si>
+  <si>
+    <t>Thanh Tri Post Office</t>
+  </si>
+  <si>
+    <t>タンチ郵便局</t>
+  </si>
+  <si>
+    <t>is_error</t>
   </si>
 </sst>
 </file>
@@ -509,16 +548,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,8 +570,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -545,8 +587,11 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -559,8 +604,11 @@
       <c r="D3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -573,8 +621,11 @@
       <c r="D4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -587,8 +638,11 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,8 +655,11 @@
       <c r="D6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,8 +672,11 @@
       <c r="D7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -629,8 +689,11 @@
       <c r="D8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -642,6 +705,60 @@
       </c>
       <c r="D9" t="s">
         <v>27</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/i18n/excel.xlsx
+++ b/src/main/resources/i18n/excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\User-Service\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54990D93-7D7F-4F74-B83A-769BE9C76A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAA1113-3355-4D68-A087-15EA3F71D6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="1710" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="33210" yWindow="2730" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>key</t>
   </si>
@@ -177,6 +177,18 @@
   </si>
   <si>
     <t>is_error</t>
+  </si>
+  <si>
+    <t>DEPARTMENTS_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Department with name {0} not found</t>
+  </si>
+  <si>
+    <t>Không tìm thấy bưu cục có tên {0}</t>
+  </si>
+  <si>
+    <t>名前が {0} の郵便局が見つかりません。</t>
   </si>
 </sst>
 </file>
@@ -548,13 +560,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -761,6 +773,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/i18n/excel.xlsx
+++ b/src/main/resources/i18n/excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\User-Service\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAA1113-3355-4D68-A087-15EA3F71D6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490B0177-7E8F-4E53-9378-087A973ACCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33210" yWindow="2730" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>

--- a/src/main/resources/i18n/excel.xlsx
+++ b/src/main/resources/i18n/excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\User-Service\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490B0177-7E8F-4E53-9378-087A973ACCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CAF7CF-4F5A-4F7D-880F-86179A8F3891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33210" yWindow="2730" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>key</t>
   </si>
@@ -189,6 +189,18 @@
   </si>
   <si>
     <t>名前が {0} の郵便局が見つかりません。</t>
+  </si>
+  <si>
+    <t>EMPTY_ROLE_LIST</t>
+  </si>
+  <si>
+    <t>Danh sách vai trò trống</t>
+  </si>
+  <si>
+    <t>Empty role list</t>
+  </si>
+  <si>
+    <t>ロールリストが空です</t>
   </si>
 </sst>
 </file>
@@ -560,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.25" bestFit="1" customWidth="1"/>
@@ -790,7 +802,25 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>